--- a/librarian_forms/012_library_equipment_rental_booking_form--librarian_forms.xlsx
+++ b/librarian_forms/012_library_equipment_rental_booking_form--librarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'bookshelf'}</t>
+          <t>bookshelf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Bookshelf'}</t>
+          <t>Bookshelf</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'desk'}</t>
+          <t>desk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Desk'}</t>
+          <t>Desk</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'denied',_'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'denied', 'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'arts_&amp;_sciences'}</t>
+          <t>arts_&amp;_sciences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Arts &amp; Sciences'}</t>
+          <t>Arts &amp; Sciences</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'humanities'}</t>
+          <t>humanities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Humanities'}</t>
+          <t>Humanities</t>
         </is>
       </c>
     </row>
